--- a/docs/xlsx/jobs-2026-08-16.xlsx
+++ b/docs/xlsx/jobs-2026-08-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="97">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,90 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Affordable Housing Manager</t>
+  </si>
+  <si>
+    <t>Community Grants, Planning &amp; Housing, LLC</t>
+  </si>
+  <si>
+    <t>Cranbury, NJ</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6dd27a97454943fb999dc304a8118193-affordable-housing-manager-community-grants-planning-housing-llc-cranbury</t>
+  </si>
+  <si>
+    <t>Become a Campus Organizer!</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>East Lansing, Michigan</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/c15affb1024a46d782dd5c29f59f4e50-become-a-campus-organizer-the-outreach-team-east-lansing</t>
+  </si>
+  <si>
+    <t>lacrosse, wi</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5432420fde5449ae998a9974850e4a2f-become-a-campus-organizer-the-outreach-team-lacrosse</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>ExpandED Schools</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 69000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d59bfd0e9b154db8b9e97faf30db77e0-development-associate-expanded-schools-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Bridges to Independence (Bridges)</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/600a2301aaa8400d88919960c06ae2aa-director-of-development-bridges-to-independence-bridges-arlington</t>
+  </si>
+  <si>
     <t>Director's Associate (Business Analyst / Strategy &amp; Operations) - Chennai Only.</t>
   </si>
   <si>
@@ -49,9 +133,6 @@
     <t>Chennai, Tamil Nadu, IN</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>INR 30000.00 - 50000.00/month</t>
   </si>
   <si>
@@ -79,6 +160,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/52ef6efa35fe4969804d22eeca5fb19c-front-desk-specialist-mountain-lion-foundation-sacramento</t>
   </si>
   <si>
+    <t>Program and Events Manager</t>
+  </si>
+  <si>
+    <t>Captain Avery Museum</t>
+  </si>
+  <si>
+    <t>Shady Side, Maryland</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1147cd393fc4147b753de580ba9625f-program-and-events-manager-captain-avery-museum-shady-side</t>
+  </si>
+  <si>
     <t>Program Coordinator – Youth Development &amp; Academic Support</t>
   </si>
   <si>
@@ -97,6 +196,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/be42ac174f974d65a52a4566f3ade50c-program-coordinator-youth-development-academic-support-youth-for-a-better-future-chicago</t>
   </si>
   <si>
+    <t>Program Counsel</t>
+  </si>
+  <si>
+    <t>Legal Services Corporation</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 122211.00 - 127148.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Philanthropy, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afbcc169095944a2bd5e003236515297-program-counsel-legal-services-corporation-washington</t>
+  </si>
+  <si>
+    <t>Program Officer for Technology</t>
+  </si>
+  <si>
+    <t>USD 108490.00 - 112873.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Veterans, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2513620ebd7f4406bc3aad8870959ae8-program-officer-for-technology-legal-services-corporation-washington</t>
+  </si>
+  <si>
+    <t>Senior Director, Research &amp; Policy</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 117000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/115c8e887b124b56a2be15ad8b9e95f1-senior-director-research-policy-expanded-schools-new-york</t>
+  </si>
+  <si>
     <t>Senior Fundraising Consultant – Campaign &amp; Donor Development</t>
   </si>
   <si>
@@ -113,6 +251,60 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/b34c8709e84345a997ccd22f67f73b24-senior-fundraising-consultant-campaign-donor-development-psychological-and-developmental-relief-society-gaza</t>
+  </si>
+  <si>
+    <t>Senior Vice President, Development and Communications</t>
+  </si>
+  <si>
+    <t>USD 148000.00 - 156000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/368dc8feabb8444da1d5176d58b6e3f1-senior-vice-president-development-and-communications-expanded-schools-new-york</t>
+  </si>
+  <si>
+    <t>Special Events Manager</t>
+  </si>
+  <si>
+    <t>Kennedy Human Rights Center</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b329ee7337fd4e86a6f8275d53e4602d-special-events-manager-kennedy-human-rights-center-new-york</t>
+  </si>
+  <si>
+    <t>Vice President of Advancement</t>
+  </si>
+  <si>
+    <t>Baltimore Community Foundation</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 195000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b2cdbf1ebc94ccc8fef84fe6f72e570-vice-president-of-advancement-baltimore-community-foundation-baltimore</t>
+  </si>
+  <si>
+    <t>Volunteer: Backend Systems &amp; Data Lead — NESA-Africa</t>
+  </si>
+  <si>
+    <t>Santos Creations Educational Foundation</t>
+  </si>
+  <si>
+    <t>Education, Environment, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/692bdcee5f9f42dc9e13a60dd6e09712-volunteer-backend-systems-data-lead-nesa-africa-santos-creations-educational-foundation-lagos</t>
   </si>
 </sst>
 </file>
@@ -594,7 +786,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -667,62 +859,361 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="H5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="C6" t="s">
         <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -732,6 +1223,19 @@
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-16.xlsx
+++ b/docs/xlsx/jobs-2026-08-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
   <si>
     <t>Title</t>
   </si>
@@ -158,6 +158,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/52ef6efa35fe4969804d22eeca5fb19c-front-desk-specialist-mountain-lion-foundation-sacramento</t>
+  </si>
+  <si>
+    <t>National Director, Corporate Partnerships and Development</t>
+  </si>
+  <si>
+    <t>Myasthenia Gravis Foundation of America</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6eeb10dd4674c22bfbb65a97483ee14-national-director-corporate-partnerships-and-development-myasthenia-gravis-foundation-of-america-westborough</t>
   </si>
   <si>
     <t>Program and Events Manager</t>
@@ -786,7 +801,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -994,165 +1009,165 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>51</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>55</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>57</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
         <v>60</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>61</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
         <v>62</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>63</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
         <v>66</v>
       </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
         <v>76</v>
       </c>
       <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
@@ -1161,10 +1176,10 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>86</v>
@@ -1178,42 +1193,65 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
         <v>89</v>
       </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>90</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
         <v>93</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>94</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" t="s">
         <v>44</v>
       </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
         <v>20</v>
       </c>
-      <c r="F18" t="s">
-        <v>95</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>96</v>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1236,6 +1274,7 @@
     <hyperlink ref="H16" r:id="rId15"/>
     <hyperlink ref="H17" r:id="rId16"/>
     <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
